--- a/output/full_scan/batch_seq7_2026-10-12.xlsx
+++ b/output/full_scan/batch_seq7_2026-10-12.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1017.186510135884</v>
+        <v>1187.186510135884</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>85</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>70.8299194581205</v>
+        <v>70.82991944907926</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>22.46357391063335</v>
+        <v>22.46357390517814</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>3.318651013588434</v>
@@ -574,27 +574,27 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6834</v>
+        <v>6742</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>804.5466989262464</v>
+        <v>1086.03584468578</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>145</v>
+        <v>63.6</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>73.21921460445134</v>
+        <v>72.10775457038606</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45.9288578548307</v>
+        <v>53.4595738685253</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.265050607775571</v>
+        <v>1.772466714000711</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2.498480163270628</v>
+        <v>0.7041814339909029</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6742</v>
+        <v>6668</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>796.0358446857816</v>
+        <v>1076.061135389728</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>63.6</v>
+        <v>55</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>72.10775471186373</v>
+        <v>73.55509788360406</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>53.4595737654702</v>
+        <v>51.3518679209731</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.772466714000711</v>
+        <v>2.374077115270643</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.7041814339428356</v>
+        <v>0.4169708477794263</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6664</v>
+        <v>6834</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>784.8525757723645</v>
+        <v>1049.546698926247</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>375</v>
+        <v>145</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>58.46313842648568</v>
+        <v>73.21921459752461</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>20.22442782894497</v>
+        <v>45.9288578548307</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.8854177535651852</v>
+        <v>2.265050607775571</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>2.386409632745616</v>
+        <v>2.498480163246599</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6782</v>
+        <v>6658</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>783.3486060982218</v>
+        <v>1037.27955606342</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>247</v>
+        <v>216</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>59.52909795904719</v>
+        <v>78.53056693231852</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>18.28530887527808</v>
+        <v>34.99376017051134</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.061105572781753</v>
+        <v>2.827955606341978</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.8008058731238878</v>
+        <v>3.943482198760682</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, williams_r_recovery, cci_momentum, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6658</v>
+        <v>6510</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>772.2795560634198</v>
+        <v>928.4217091205736</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>216</v>
+        <v>3420</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>78.53056696566851</v>
+        <v>57.20577052768977</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>34.99376013057073</v>
+        <v>21.31477911075094</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.827955606341978</v>
+        <v>1.803685229646256</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>3.943482199121227</v>
+        <v>-16.13742271907553</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6510</v>
+        <v>6715</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>758.4217091205735</v>
+        <v>925.6315000133324</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3420</v>
+        <v>501</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>57.2057705487402</v>
+        <v>66.16964415523616</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>21.31477908094337</v>
+        <v>28.61797359303317</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.803685229646256</v>
+        <v>0.979950976684418</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-16.13742271787377</v>
+        <v>5.009554865577421</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6715</v>
+        <v>6782</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>755.6315000133324</v>
+        <v>923.3486060982218</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>501</v>
+        <v>247</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>66.16964416836245</v>
+        <v>59.52909793578493</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>28.61797356841543</v>
+        <v>18.28530884793782</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.979950976684418</v>
+        <v>3.061105572781753</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>5.009554865216924</v>
+        <v>-0.8008058730036947</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, williams_r_recovery, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6668</v>
+        <v>6505</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>746.0611353897284</v>
+        <v>856.8807482701463</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>55</v>
+        <v>108.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>73.555097940707</v>
+        <v>74.180853029234</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>51.35186792097311</v>
+        <v>60.423202008186</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.374077115270643</v>
+        <v>1.41851779215898</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.4169708479596856</v>
+        <v>1.602567569523862</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6491</v>
+        <v>6835</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>735.2971359469873</v>
+        <v>852.113925569208</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>409.5</v>
+        <v>32.6</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>56.38819692935826</v>
+        <v>65.95093880792113</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>28.42757032126515</v>
+        <v>22.69131680718577</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.8227404356064368</v>
+        <v>1.507881847975112</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.9999094237301788</v>
+        <v>0.1731992419525788</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6835</v>
+        <v>6534</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>712.1139255692268</v>
+        <v>839.6431009495623</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>32.6</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>65.95093878576569</v>
+        <v>65.10946895535621</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>22.69131684301217</v>
+        <v>24.55138480365569</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.507881847975112</v>
+        <v>2.846296842800895</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.1731992419165282</v>
+        <v>0.5510468149021857</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6743</v>
+        <v>6811</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>710.8517715284296</v>
+        <v>814.7026466707176</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>32.35</v>
+        <v>275.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>55.28064060118927</v>
+        <v>67.67565170458286</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>38.71877075883105</v>
+        <v>37.13948868757406</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.278962854753346</v>
+        <v>0.8533606805252061</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,11 +1153,11 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.2335929673216628</v>
+        <v>3.018811658559451</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>690.711937481825</v>
+        <v>805.711937481825</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>747</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>60.66189341786837</v>
+        <v>60.66189336887263</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>33.92026131131691</v>
+        <v>33.92026132108649</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1.352157786709575</v>
@@ -1200,17 +1200,17 @@
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>12.74501962810635</v>
+        <v>12.74501962750555</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>686.8917725807322</v>
+        <v>801.8917725807322</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>783</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>58.30662299915769</v>
+        <v>58.30662292232546</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>36.4231132519006</v>
+        <v>36.42311328825775</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0.5216179435744679</v>
@@ -1253,37 +1253,37 @@
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-2.601287525307498</v>
+        <v>-2.601287526509232</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6706</v>
+        <v>6664</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>672.1715044577987</v>
+        <v>784.8525757723647</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>153.5</v>
+        <v>375</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,49 +1294,49 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>58.7023938853292</v>
+        <v>58.46313838419255</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>52.14414450943144</v>
+        <v>20.22442781128736</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.3354864842086537</v>
+        <v>0.8854177535651852</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.5076761540571759</v>
+        <v>2.386409630822798</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6530</v>
+        <v>6504</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>653.8929113371468</v>
+        <v>769</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>95.90000000000001</v>
+        <v>39.05</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>50.01769871340625</v>
+        <v>56.47278304262821</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>29.63517487110819</v>
+        <v>34.58957019830961</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.2393399544252789</v>
+        <v>11.57605425506843</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-1.015218982431321</v>
+        <v>0.345092191358596</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6538</v>
+        <v>6491</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>641.9971705368591</v>
+        <v>735.2971359469873</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>303</v>
+        <v>409.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>45.33012721826575</v>
+        <v>56.38819689283168</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>40.39622574022695</v>
+        <v>28.42757032451091</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.431815634049077</v>
+        <v>0.8227404356064368</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-15.7273474604519</v>
+        <v>-0.9999094240907364</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6683</v>
+        <v>6598</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>616.5797014989881</v>
+        <v>723.4872055535474</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1440</v>
+        <v>28.3</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>49.35143136708182</v>
+        <v>55.84243681480102</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>16.06971696176983</v>
+        <v>12.18053001962004</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.5545862549957236</v>
+        <v>1.181707405523063</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-22.85536866248106</v>
+        <v>0.0545205144324424</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6811</v>
+        <v>6743</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>614.7026466707176</v>
+        <v>710.8517715284296</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>275.5</v>
+        <v>32.35</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>67.67565175804404</v>
+        <v>55.28064047168935</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>37.13948867069421</v>
+        <v>38.7187707630252</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.8533606805252061</v>
+        <v>2.278962854753346</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>3.018811658679639</v>
+        <v>0.2335929674538512</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6534</v>
+        <v>6706</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>614.6431009495643</v>
+        <v>682.1715044577986</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>94.59999999999999</v>
+        <v>153.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>65.10946882134202</v>
+        <v>58.70239387561176</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>24.55138486988091</v>
+        <v>52.14414458792989</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.846296842800895</v>
+        <v>0.3354864842086537</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.5510468149021857</v>
+        <v>-0.5076761542975206</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6532</v>
+        <v>6556</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>611.9313989614537</v>
+        <v>675.5335028162589</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>106</v>
+        <v>62.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>53.10246736474582</v>
+        <v>56.797085084856</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>44.04830989801336</v>
+        <v>9.573743647868692</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.4971977385086653</v>
+        <v>4.856107465658216</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.2652690400521278</v>
+        <v>0.1623504524133998</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6693</v>
+        <v>6667</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>572.9517666872712</v>
+        <v>674.40390176609</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>201.5</v>
+        <v>274</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>54.60321742350973</v>
+        <v>63.68255288002151</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>24.81268471751862</v>
+        <v>45.40832741670485</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.4117955085664724</v>
+        <v>1.310579097888679</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.2565876127056992</v>
+        <v>1.513313309293396</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6643</v>
+        <v>6716</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>572.6681455180096</v>
+        <v>671.1726021906051</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>476.5</v>
+        <v>125</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>50.89505735779525</v>
+        <v>50.79773524677783</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>33.85585105196407</v>
+        <v>34.37235963727744</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.5353714370107813</v>
+        <v>0.2172602190605015</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-2.075230876726117</v>
+        <v>1.668573735301827</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6505</v>
+        <v>6530</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>571.8807482701463</v>
+        <v>653.8929113371468</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>108.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>74.18085304899944</v>
+        <v>50.01769867250501</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>60.42320195641929</v>
+        <v>29.63517487110819</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.41851779215898</v>
+        <v>0.2393399544252789</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.602567569680084</v>
+        <v>-1.01521898312832</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6598</v>
+        <v>6538</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>563.4872055535474</v>
+        <v>641.9971705368591</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>28.3</v>
+        <v>303</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>55.84243678749207</v>
+        <v>45.33012721713903</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>12.18053016372573</v>
+        <v>40.39622577196214</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.181707405523063</v>
+        <v>1.431815634049077</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.0545205144925282</v>
+        <v>-15.72734746074037</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6556</v>
+        <v>6722</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>560.5335028162589</v>
+        <v>623.5501139374574</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>62.5</v>
+        <v>33.35</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>56.79708498167165</v>
+        <v>59.81617500570657</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>9.573743495251207</v>
+        <v>26.02773159141732</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>4.856107465658216</v>
+        <v>0.7881702324407012</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1623504528460267</v>
+        <v>0.110116895820011</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6716</v>
+        <v>6690</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>556.1726021906049</v>
+        <v>621.9315060239612</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>125</v>
+        <v>179.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>50.79773524410402</v>
+        <v>59.15120639480954</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>34.37235948143008</v>
+        <v>35.86611631262531</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.2172602190605015</v>
+        <v>0.2571500425939381</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.668573735626294</v>
+        <v>-0.4651637099113621</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6805</v>
+        <v>6683</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>546.2623894279382</v>
+        <v>616.5797014989881</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>2270</v>
+        <v>1440</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>49.62243589776076</v>
+        <v>49.35143133956718</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>34.61614770868827</v>
+        <v>16.06971688318523</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.192278689698968</v>
+        <v>0.5545862549957236</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-28.0768049138541</v>
+        <v>-22.85536866055821</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6577</v>
+        <v>6669</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>538.7530336455887</v>
+        <v>611.9735108009545</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>80.40000000000001</v>
+        <v>2275</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,49 +2036,49 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>52.54028410602609</v>
+        <v>33.41569263102473</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>11.56657042285801</v>
+        <v>43.18543237726884</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2.018060115491726</v>
+        <v>0.8353429280907697</v>
       </c>
       <c r="K30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0872970021441052</v>
+        <v>152.6539112004195</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6667</v>
+        <v>6532</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>534.4039017660899</v>
+        <v>611.9313989614537</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>274</v>
+        <v>106</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>63.68255297809196</v>
+        <v>53.1024673437158</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45.40832741519156</v>
+        <v>44.04830992584014</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.310579097888679</v>
+        <v>0.4971977385086653</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>1.513313309053048</v>
+        <v>-0.2652690399800299</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6654</v>
+        <v>6807</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>531.6662761290031</v>
+        <v>611.5144498940665</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>213.5</v>
+        <v>33.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>56.31404827416053</v>
+        <v>51.89901944601297</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>30.26212655170768</v>
+        <v>12.06975502514222</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.9685837489420042</v>
+        <v>1.750224174313651</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,51 +2160,51 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.2667298734933645</v>
+        <v>0.226125084845449</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6806</v>
+        <v>6830</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>610.0130081812625</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>3.51</v>
+        <v>540</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>31.69494290248666</v>
+        <v>52.76964355109528</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>32.59382456590206</v>
+        <v>23.21538487854609</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.6150814924832095</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.4112814278470682</v>
+        <v>-4.577019244752925</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6504</v>
+        <v>6792</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>519</v>
+        <v>609.0442378262532</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>39.05</v>
+        <v>60.1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>56.47278298031825</v>
+        <v>54.79708848523555</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>34.58957018106578</v>
+        <v>33.35043360645724</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>11.57605425506843</v>
+        <v>1.530979267165331</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.3450921916229716</v>
+        <v>0.130577529718983</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6690</v>
+        <v>6788</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>506.9315060239613</v>
+        <v>607.9028794213714</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>179.5</v>
+        <v>368.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>59.15120641333002</v>
+        <v>58.23141582627196</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>35.86611622732337</v>
+        <v>21.0181224491698</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.2571500425939381</v>
+        <v>2.033126194885665</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.4651637093104979</v>
+        <v>4.472215227817674</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6485</v>
+        <v>6640</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>505.3487331955238</v>
+        <v>606.2444031295571</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>1155</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>58.67643035550372</v>
+        <v>54.891561431295</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>38.287533372535</v>
+        <v>19.51822258242198</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7333531829555759</v>
+        <v>1.227560151298136</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1.011231697683789</v>
+        <v>-0.7652002440163654</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6830</v>
+        <v>6591</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>500.0130081812626</v>
+        <v>590.148738933833</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>540</v>
+        <v>42.6</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>52.76964359228754</v>
+        <v>46.89335827319575</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>23.21538492668514</v>
+        <v>29.01496572782882</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6150814924832095</v>
+        <v>1.92993831360166</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-4.577019244752925</v>
+        <v>-0.0803833152428518</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6674</v>
+        <v>6693</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>499.2212274787</v>
+        <v>572.9517666872712</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>18.3</v>
+        <v>201.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>68.82233493789985</v>
+        <v>54.60321742639136</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>40.74217823811154</v>
+        <v>24.81268482600295</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3936509702720014</v>
+        <v>0.4117955085664724</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0364317243843081</v>
+        <v>-0.2565876127537549</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6488</v>
+        <v>6643</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>497.6859264276306</v>
+        <v>572.6681455180095</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1115</v>
+        <v>476.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>58.25217373597128</v>
+        <v>50.89505734925093</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>21.24533949043256</v>
+        <v>33.85585100096777</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.7315656439196571</v>
+        <v>0.5353714370107813</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>18.80400497144533</v>
+        <v>-2.075230877927865</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6792</v>
+        <v>6805</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>494.0442378262519</v>
+        <v>566.3187136528276</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>60.1</v>
+        <v>2270</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>54.79708855977928</v>
+        <v>49.62243590523882</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>33.35043366714826</v>
+        <v>34.61614761415959</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.530979267165331</v>
+        <v>1.19968494533798</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.1305775295026719</v>
+        <v>-28.07680492827511</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6788</v>
+        <v>6831</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>492.9028794213714</v>
+        <v>560.2465108001369</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>368.5</v>
+        <v>492.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>58.23141596416532</v>
+        <v>41.23887068165126</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>21.01812239496272</v>
+        <v>25.74404804298588</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.033126194885665</v>
+        <v>0.834131500795728</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>4.472215227697454</v>
+        <v>2.18803692924746</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6640</v>
+        <v>6789</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>491.2444031295566</v>
+        <v>547.566510734224</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1155</v>
+        <v>470.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,49 +2672,49 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>54.89156149111169</v>
+        <v>50.5054631166804</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>19.51822264884904</v>
+        <v>17.68578405710346</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.227560151298136</v>
+        <v>0.5686795300033283</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.7652002478619595</v>
+        <v>0.5061557766669544</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6722</v>
+        <v>6577</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>488.5501139374596</v>
+        <v>538.7530336455887</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>33.35</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>59.81617512521088</v>
+        <v>52.54028399821141</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>26.02773154004941</v>
+        <v>11.56657040401505</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7881702324407012</v>
+        <v>2.018060115491726</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.1101168957719416</v>
+        <v>0.0872970022883006</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6591</v>
+        <v>6531</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>480.1487389339224</v>
+        <v>533.9652939393995</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>42.6</v>
+        <v>947</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,49 +2778,49 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>46.8933580034145</v>
+        <v>48.70759541821682</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>29.01496488951406</v>
+        <v>14.46830292813745</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.92993831360166</v>
+        <v>1.415667815902723</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M44" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.0803833157475795</v>
+        <v>-1.843437254621506</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6807</v>
+        <v>6654</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>471.5144498940663</v>
+        <v>531.6662761290031</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>33.5</v>
+        <v>213.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>51.89901944413669</v>
+        <v>56.31404825888895</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>12.06975503985134</v>
+        <v>30.26212658569749</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.750224174313651</v>
+        <v>0.9685837489420042</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,48 +2849,48 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.226125084893513</v>
+        <v>0.2667298736135421</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6589</v>
+        <v>6806</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>470.4796846288954</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>50.1</v>
+        <v>3.51</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G46" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>48.6243175062868</v>
+        <v>31.69496066993881</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>21.24509239129652</v>
+        <v>32.59380893356278</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.7561113192874728</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.1940019393198087</v>
+        <v>0.4112811360301456</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6768</v>
+        <v>6597</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>466.608917344366</v>
+        <v>528.6326404226616</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>64.5</v>
+        <v>73</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>54.49960064486088</v>
+        <v>53.13172804593628</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22.19397668690831</v>
+        <v>7.093351423109127</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.3425971401110147</v>
+        <v>2.189236184740659</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.3852996843391737</v>
+        <v>0.5817230257401911</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6525</v>
+        <v>6770</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>441.1887908533906</v>
+        <v>521.8706509379772</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>138</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,49 +2990,49 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>52.46872787849292</v>
+        <v>48.01691836753731</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>14.2123793074935</v>
+        <v>12.85976644654291</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6860544895835828</v>
+        <v>0.4709563356880682</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M48" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>1.039781305725228</v>
+        <v>-0.2864837187962461</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6669</v>
+        <v>6485</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>440.970722948707</v>
+        <v>505.3487331955211</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2275</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>33.41569269649493</v>
+        <v>58.67643033388285</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>43.18543236192065</v>
+        <v>38.28753350764155</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.758100650478691</v>
+        <v>0.7333531829555759</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>152.6539112292612</v>
+        <v>1.011231697467493</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6531</v>
+        <v>6674</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>433.9652939393992</v>
+        <v>499.2212274787</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>947</v>
+        <v>18.3</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>48.70759541475464</v>
+        <v>68.82233442983807</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>14.46830285615817</v>
+        <v>40.74217840841375</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.415667815902723</v>
+        <v>0.3936509702720014</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-1.843437253299552</v>
+        <v>0.0364317245886027</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6515</v>
+        <v>6488</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>431.7307837976265</v>
+        <v>497.6839960964744</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>6025</v>
+        <v>1115</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>47.52218867293121</v>
+        <v>58.25217373296208</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>11.09474957255425</v>
+        <v>21.24533951235784</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.561167391388858</v>
+        <v>0.7331367103441004</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-3.977767713892462</v>
+        <v>18.80400497108491</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, williams_r_recovery</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6831</v>
+        <v>6589</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>430.246510800136</v>
+        <v>470.4796846288954</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>492.5</v>
+        <v>50.1</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>41.23887068529113</v>
+        <v>48.6243175062868</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>25.74404797862577</v>
+        <v>21.24509246571593</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.834131500795728</v>
+        <v>0.7561113192874728</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>2.188036930208803</v>
+        <v>-0.1940019393678754</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6695</v>
+        <v>6768</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>427.8870168861649</v>
+        <v>466.6089173443658</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>51</v>
+        <v>64.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>50.57017937562686</v>
+        <v>54.49960097580833</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>23.00959640253052</v>
+        <v>22.19397662811261</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.6781221367930748</v>
+        <v>0.3425971401110147</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.04749877458283</v>
+        <v>0.3852996837383138</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6582</v>
+        <v>6541</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>425.2308519409057</v>
+        <v>462.8899970801408</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>31.8</v>
+        <v>33.3</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>55.58318121784156</v>
+        <v>54.02381869140967</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>15.4283124961189</v>
+        <v>22.93535162724842</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.560709839876767</v>
+        <v>0.6894921804557577</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0980181221623449</v>
+        <v>0.5621326490264952</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6770</v>
+        <v>6515</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>421.8706509379771</v>
+        <v>461.7307837976266</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>6025</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,49 +3361,49 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>48.01691838468744</v>
+        <v>47.52218865869804</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>12.85976644005756</v>
+        <v>11.09474961613859</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.4709563356880682</v>
+        <v>1.561167391388858</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.2864837187962461</v>
+        <v>-3.977767719900868</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6561</v>
+        <v>6525</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>417.7069975539561</v>
+        <v>441.1887908533906</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>308.5</v>
+        <v>138</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,49 +3414,49 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>39.43795003768385</v>
+        <v>52.46872787849292</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>20.69953653410569</v>
+        <v>14.21237934691604</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.561578366171578</v>
+        <v>0.6860544895835828</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.1750405533878614</v>
+        <v>1.039781305508908</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6799</v>
+        <v>6657</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>415.0007611595098</v>
+        <v>437.8709867264517</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>88.2</v>
+        <v>33.85</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.93560901372651</v>
+        <v>54.15017766392874</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>33.22269409275544</v>
+        <v>24.13200282604445</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.9090067923013468</v>
+        <v>0.5027935362691578</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.3261065042215252</v>
+        <v>0.0453804217751918</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6761</v>
+        <v>6771</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>411.1349101039444</v>
+        <v>437.3297998659871</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>167</v>
+        <v>41.75</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>47.44662400450127</v>
+        <v>46.26128216499151</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>12.97081634466955</v>
+        <v>18.55895777585377</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.038930402669543</v>
+        <v>0.2593117203180975</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.5754147943427199</v>
+        <v>-0.08167405674717231</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6763</v>
+        <v>6695</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>403.666817281946</v>
+        <v>427.8870168861649</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>41.55</v>
+        <v>51</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.02671479235777</v>
+        <v>50.57017934869458</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>16.92655943006228</v>
+        <v>23.00959643943206</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.8758410685405037</v>
+        <v>0.6781221367930748</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0746624485966519</v>
+        <v>-0.0474987747630908</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6585</v>
+        <v>6582</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>395.5763188641815</v>
+        <v>425.2308519409053</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>31.8</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>32.31524258479303</v>
+        <v>55.58318111922279</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>32.75730811399979</v>
+        <v>15.42831250287054</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.829964727802949</v>
+        <v>0.560709839876767</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.068737011859155</v>
+        <v>0.0980181221503308</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6796</v>
+        <v>6561</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>386.0113214614027</v>
+        <v>417.7069975539561</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>56</v>
+        <v>308.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,49 +3679,49 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>53.28524496848229</v>
+        <v>39.43794957430431</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>21.28244698720317</v>
+        <v>20.69953657519454</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.2548826807025662</v>
+        <v>1.561578366171578</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.7423216490709893</v>
+        <v>0.175040555070236</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6655</v>
+        <v>6799</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>376.0158499662728</v>
+        <v>415.0007611595098</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>126.5</v>
+        <v>88.2</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>52.15540238584001</v>
+        <v>54.93560897704307</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>10.71481446558834</v>
+        <v>33.22269412950025</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.7365576196625936</v>
+        <v>0.9090067923013468</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>3.570681429180747</v>
+        <v>0.3261065036927486</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6588</v>
+        <v>6761</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>367.0723230053806</v>
+        <v>411.1349101039444</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>102.5</v>
+        <v>167</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>42.75049442079275</v>
+        <v>47.44662402853478</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>19.29890898858704</v>
+        <v>12.97081635146906</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.4196724820302839</v>
+        <v>1.038930402669543</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-1.309301162993457</v>
+        <v>0.5754147939822176</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6771</v>
+        <v>6560</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>362.3297998659871</v>
+        <v>410.881593626097</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>41.75</v>
+        <v>32.95</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>46.26128220204876</v>
+        <v>52.23816064691894</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>18.55895774248163</v>
+        <v>12.0347071433329</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.2593117203180975</v>
+        <v>0.5957775099235774</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.08167405674717231</v>
+        <v>-0.020227368286897</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6517</v>
+        <v>6757</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>361.7414910441248</v>
+        <v>405.0753288398563</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>65</v>
+        <v>53.6</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>48.78771320848568</v>
+        <v>45.74153427178891</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>14.09446288308754</v>
+        <v>15.45717900473197</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.9128737243950188</v>
+        <v>0.8797268738980761</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.3238595240574191</v>
+        <v>0.0575041882058702</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6821</v>
+        <v>6763</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>354.2064665581736</v>
+        <v>403.6668172819355</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>44</v>
+        <v>41.55</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>54.88103088880244</v>
+        <v>52.02671453766379</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>27.12906232462466</v>
+        <v>16.92655941738681</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.28447461454291</v>
+        <v>0.8758410685405037</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>3</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.4453156185254955</v>
+        <v>0.074662448476484</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6684</v>
+        <v>6585</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>346.2255620749152</v>
+        <v>395.5763188641816</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>47.5</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>45.77390752333616</v>
+        <v>32.31524256940166</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>25.99315965946456</v>
+        <v>32.75730811494054</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.3636937642175737</v>
+        <v>1.829964727802949</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.1323880390833816</v>
+        <v>-0.0687370120994952</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6494</v>
+        <v>6645</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>345.330462394593</v>
+        <v>386.2454943191318</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>49.75</v>
+        <v>13</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>38.35432693183119</v>
+        <v>53.3928159219853</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10.5510297917086</v>
+        <v>23.36403850905613</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.65109138223515</v>
+        <v>3.706842810709068</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0213205769270174</v>
+        <v>0.07833275367442979</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6789</v>
+        <v>6796</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>342.5665107342246</v>
+        <v>386.0113214614027</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>470.5</v>
+        <v>56</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>50.50546340193206</v>
+        <v>53.28524546117224</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>17.68578408709973</v>
+        <v>21.28244692857131</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.5686795300033283</v>
+        <v>0.2548826807025662</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.5061557731818827</v>
+        <v>0.7423216472443593</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6823</v>
+        <v>6655</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>340.543206452588</v>
+        <v>376.0158499662728</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>59.4</v>
+        <v>126.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>43.24186926470246</v>
+        <v>52.1554023846087</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>20.77553687739429</v>
+        <v>10.71481446580575</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.937148462846617</v>
+        <v>0.7365576196625936</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0479925011538771</v>
+        <v>3.570681429060572</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6670</v>
+        <v>6588</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>339.6963447006751</v>
+        <v>367.0723230053806</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>272</v>
+        <v>102.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>49.42410582385731</v>
+        <v>42.75049438805971</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>19.29764617098144</v>
+        <v>19.29890903642579</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>2.277972203475988</v>
+        <v>0.4196724820302839</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.0164146889854667</v>
+        <v>-1.309301162777135</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6739</v>
+        <v>6517</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>338.5454440575367</v>
+        <v>361.7414910441247</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>1075</v>
+        <v>65</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>46.71219626454592</v>
+        <v>48.78771322597999</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>9.86578851509039</v>
+        <v>14.09446301533323</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.2594428329195269</v>
+        <v>0.9128737243950188</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-7.171386521269118</v>
+        <v>0.3238595235526924</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6725</v>
+        <v>6821</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>332.7583495876115</v>
+        <v>354.2064665581736</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>213</v>
+        <v>44</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>40.35946531274086</v>
+        <v>54.88103082292425</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.52675701232253</v>
+        <v>27.12906232462465</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.196763676680914</v>
+        <v>1.28447461454291</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.9030546459697036</v>
+        <v>0.4453156185134741</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, dealer_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6689</v>
+        <v>6684</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>330.545825862222</v>
+        <v>346.2255620749166</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>64.2</v>
+        <v>47.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.97587147228896</v>
+        <v>45.77390752333616</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>23.05833532100002</v>
+        <v>25.99315972123763</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.2742830389809332</v>
+        <v>0.3636937642175737</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.2860835691396207</v>
+        <v>-0.1323880394438996</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6597</v>
+        <v>6494</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>328.6326404226616</v>
+        <v>345.3304623945947</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>73</v>
+        <v>49.75</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>53.13172805370884</v>
+        <v>38.35432691089398</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>7.093351410297553</v>
+        <v>10.55102975682072</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>2.189236184740659</v>
+        <v>1.65109138223515</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.5817230261006991</v>
+        <v>0.0213205769630688</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6719</v>
+        <v>6823</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>324.4455647066545</v>
+        <v>340.543206452588</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>187</v>
+        <v>59.4</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>46.69738727353806</v>
+        <v>43.24186901400879</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16.52729343756785</v>
+        <v>20.77553688817692</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.287443840765432</v>
+        <v>1.937148462846617</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>1.452589656406973</v>
+        <v>0.0479925005289715</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6558</v>
+        <v>6670</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>323.9410109380734</v>
+        <v>339.6963447006751</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>24.6</v>
+        <v>272</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,49 +4527,49 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>47.48146736146364</v>
+        <v>49.42410587150288</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>24.38653136036908</v>
+        <v>19.29764639456572</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.7024019985488166</v>
+        <v>2.277972203475988</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0885208216770228</v>
+        <v>-0.0164146889854667</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6657</v>
+        <v>6739</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>322.8709867264517</v>
+        <v>338.5454440575372</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>33.85</v>
+        <v>1075</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>54.15017779652766</v>
+        <v>46.71219618682257</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>24.13200278444529</v>
+        <v>9.865788513915932</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5027935362691578</v>
+        <v>0.2594428329195269</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0453804217992293</v>
+        <v>-7.171386517183247</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6641</v>
+        <v>6725</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>321.7582906906518</v>
+        <v>332.7583495876115</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>17.25</v>
+        <v>213</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>52.08940429753648</v>
+        <v>40.35946501278444</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>8.265223093385721</v>
+        <v>15.52675711869712</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5037607475910363</v>
+        <v>1.196763676680914</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.1460165380744533</v>
+        <v>0.9030546486134972</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6584</v>
+        <v>6689</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>317.59332732356</v>
+        <v>330.545825862222</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>522</v>
+        <v>64.2</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>39.21630599435985</v>
+        <v>51.97587142770416</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>17.61122880050586</v>
+        <v>23.05833533787997</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4505372838055244</v>
+        <v>0.2742830389809332</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-1.358094535946115</v>
+        <v>-0.2860835695241804</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6753</v>
+        <v>6776</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>311.3295619012239</v>
+        <v>325.2828735629636</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>126.5</v>
+        <v>52.9</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>32.03244193115935</v>
+        <v>53.52886998819773</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>12.13947975801796</v>
+        <v>12.65071126402254</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>2.108104509723941</v>
+        <v>1.038419871846831</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.2535988108774474</v>
+        <v>0.1213553881016105</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6781</v>
+        <v>6719</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>301.1456279837396</v>
+        <v>324.4455647066545</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>1015</v>
+        <v>187</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45.27931895661547</v>
+        <v>46.69738715890255</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>9.548502676403531</v>
+        <v>16.52729346504806</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6665250593251153</v>
+        <v>1.287443840765432</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>2.65923749144687</v>
+        <v>1.452589656166658</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6692</v>
+        <v>6558</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>298.2814679347693</v>
+        <v>323.9410109380822</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>22.85</v>
+        <v>24.6</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>50.48429725672904</v>
+        <v>47.48146714516093</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>6.62999837432783</v>
+        <v>24.38653148488022</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.5772933387533363</v>
+        <v>0.7024019985488166</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.09102036109430781</v>
+        <v>0.0885208214847444</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6550</v>
+        <v>6641</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>297.2553063214768</v>
+        <v>321.7582906906518</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>16.35</v>
+        <v>17.25</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>68.36293730828308</v>
+        <v>52.08940430478288</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>34.87527282354441</v>
+        <v>8.265223093385718</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.3989913810905692</v>
+        <v>0.5037607475910363</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.3988587440899107</v>
+        <v>0.1460165380744533</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6560</v>
+        <v>6584</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>295.8815936260972</v>
+        <v>317.59332732356</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>32.95</v>
+        <v>522</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>52.23816059840088</v>
+        <v>39.21630597041703</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>12.0347071433329</v>
+        <v>17.61122877808091</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.5957775099235774</v>
+        <v>0.4505372838055244</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.020227368202782</v>
+        <v>-1.358094537868928</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6757</v>
+        <v>6753</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>295.0753288398561</v>
+        <v>311.3295619012238</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>53.6</v>
+        <v>126.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>45.74153414602189</v>
+        <v>32.03244185314959</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15.45717898054404</v>
+        <v>12.13947977921719</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.8797268738980761</v>
+        <v>2.108104509723941</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0575041884462144</v>
+        <v>-0.2535988111177787</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6642</v>
+        <v>6579</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>292.3062367008106</v>
+        <v>304.877488895375</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>76.2</v>
+        <v>151</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>41.28496442120246</v>
+        <v>45.36640887426356</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>18.952178462483</v>
+        <v>16.44705736298143</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.360940434385206</v>
+        <v>0.6051100890026031</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.2640077568249063</v>
+        <v>-0.2063672879692194</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6754</v>
+        <v>6781</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>291.3030299038639</v>
+        <v>301.1456279837396</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>42</v>
+        <v>1015</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>52.72558962054487</v>
+        <v>45.27931893745896</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14.05934687311265</v>
+        <v>9.548502663513856</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.023429854995107</v>
+        <v>0.6665250593251153</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0273985368990826</v>
+        <v>2.659237480631095</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6651</v>
+        <v>6692</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>290.6117831027684</v>
+        <v>298.2814679347693</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>141.5</v>
+        <v>22.85</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>44.30469270004493</v>
+        <v>50.48429718471372</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>16.18606366173393</v>
+        <v>6.62999825997055</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6019138272576053</v>
+        <v>0.5772933387533363</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-1.201562306981661</v>
+        <v>0.09102036145482501</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6756</v>
+        <v>6550</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>289.9922713875138</v>
+        <v>297.2553063214768</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>96.09999999999999</v>
+        <v>16.35</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>44.56775284585899</v>
+        <v>68.36293734460926</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14.32305894123797</v>
+        <v>34.8752736840302</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.9947443426038524</v>
+        <v>0.3989913810905692</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0587384166942641</v>
+        <v>0.3988587454248047</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6579</v>
+        <v>6642</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>284.877488895375</v>
+        <v>292.3062367008106</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>151</v>
+        <v>76.2</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>45.3664089416412</v>
+        <v>41.28496443771858</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>16.44705737871091</v>
+        <v>18.95217844855031</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6051100890026031</v>
+        <v>1.360940434385206</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.2063672879692194</v>
+        <v>-0.2640077568970074</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6581</v>
+        <v>6754</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>278.9350312199462</v>
+        <v>291.3030299038641</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>45.4432201173999</v>
+        <v>52.72558970939033</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>13.11385881943677</v>
+        <v>14.05934677963347</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.3665781368486499</v>
+        <v>1.023429854995107</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.154087964960388</v>
+        <v>0.0273985366226884</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6741</v>
+        <v>6651</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>278.8186104191963</v>
+        <v>290.6117831027684</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>54</v>
+        <v>141.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>30.82878289980829</v>
+        <v>44.30469270004493</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>30.09866949199544</v>
+        <v>16.18606372339761</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.60536979701997</v>
+        <v>0.6019138272576053</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.3101348157746411</v>
+        <v>-1.201562307149929</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6645</v>
+        <v>6756</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>276.2454943191318</v>
+        <v>289.9922713875139</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>13</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>53.39281587123691</v>
+        <v>44.56775283172526</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>23.36403837851731</v>
+        <v>14.32305903692639</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>3.706842810709068</v>
+        <v>0.9947443426038524</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.07833275372249759</v>
+        <v>-0.0587384172230255</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6829</v>
+        <v>6680</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>273.7032980820721</v>
+        <v>284.8014538247241</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>207.5</v>
+        <v>50.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>45.03584744696556</v>
+        <v>51.86727299817985</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>9.599296893967219</v>
+        <v>6.987106085145139</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.2885030873488128</v>
+        <v>1.044923357110335</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.3300057046523754</v>
+        <v>-0.1442439727388986</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, stronger_than_market, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6671</v>
+        <v>6581</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>270.7997222704713</v>
+        <v>278.9350312199471</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>22.9</v>
+        <v>108</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>47.71294335781618</v>
+        <v>45.4432199195223</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16.09590059662493</v>
+        <v>13.11385872933066</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>2.108807611928846</v>
+        <v>0.3665781368486499</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.023058181749265</v>
+        <v>-0.1540879647200507</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6666</v>
+        <v>6741</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>268.7627300524609</v>
+        <v>278.8186104191965</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>43.6</v>
+        <v>54</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>38.73312160639838</v>
+        <v>30.82878277988961</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>15.68723446310355</v>
+        <v>30.09866944335402</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.294527964597612</v>
+        <v>1.60536979701997</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.2070725309191121</v>
+        <v>-0.3101348159188487</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6541</v>
+        <v>6829</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>262.8899970801408</v>
+        <v>273.703298082072</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>33.3</v>
+        <v>207.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>54.02381875448695</v>
+        <v>45.03584744231772</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>22.9353515749611</v>
+        <v>9.599296956241078</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.6894921804557577</v>
+        <v>0.2885030873488128</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.5621326491466678</v>
+        <v>-0.3300057054936065</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6498</v>
+        <v>6552</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>245.6456138915675</v>
+        <v>272.1497172619781</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>68.90000000000001</v>
+        <v>24</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>46.11464199239819</v>
+        <v>42.29435048698538</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>17.34108826104206</v>
+        <v>16.52592985665514</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.289216213874881</v>
+        <v>1.28961732823261</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.8693737156100791</v>
+        <v>0.0161780277665954</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6735</v>
+        <v>6671</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>234.9142746095371</v>
+        <v>270.7997222704713</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>62.2</v>
+        <v>22.9</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>43.33955106062101</v>
+        <v>47.71294343873937</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>21.78086284250299</v>
+        <v>16.09590075803724</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.555645344978061</v>
+        <v>2.108807611928846</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.061726410913816</v>
+        <v>0.0230581816531245</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6614</v>
+        <v>6666</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>219.1820364645796</v>
+        <v>268.7627300524609</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>35.15</v>
+        <v>43.6</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>41.50279353059778</v>
+        <v>38.73312111208121</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>21.86905429803516</v>
+        <v>15.68723463408798</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.14782851776032</v>
+        <v>1.294527964597612</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0173256256338899</v>
+        <v>-0.2070725309191121</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6776</v>
+        <v>6498</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>215.2828735629637</v>
+        <v>245.6456138915675</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>52.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>53.52886994107286</v>
+        <v>46.11464196033085</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>12.6507112017077</v>
+        <v>17.34108832828982</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.038419871846831</v>
+        <v>1.289216213874881</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.1213553881496821</v>
+        <v>0.8693737148890401</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6570</v>
+        <v>6614</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>214.4958748977889</v>
+        <v>239.1820364645794</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>46.7</v>
+        <v>35.15</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>36.83266518716791</v>
+        <v>41.50279168050669</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.14034538783397</v>
+        <v>21.8690546455854</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.081805088054363</v>
+        <v>1.14782851776032</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.1898946634581333</v>
+        <v>0.0173256270999997</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6512</v>
+        <v>6735</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>211.2221389265453</v>
+        <v>234.9142746095368</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>20.2</v>
+        <v>62.2</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>51.95883667456395</v>
+        <v>43.33955106939973</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>8.065188823726656</v>
+        <v>21.78086284754329</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.782691486916839</v>
+        <v>0.555645344978061</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0363407266449023</v>
+        <v>-0.0617264109258217</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6486</v>
+        <v>6570</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>209.5947783611973</v>
+        <v>214.4958748977889</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>77.7</v>
+        <v>46.7</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>39.93525966400193</v>
+        <v>36.83266519192125</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>34.33063995525251</v>
+        <v>18.14034540569269</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.8023927959619278</v>
+        <v>1.081805088054363</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.526272577917686</v>
+        <v>0.1898946633980431</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6606</v>
+        <v>6512</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>208.2924315520955</v>
+        <v>211.2221389265453</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>24.4</v>
+        <v>20.2</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>41.5137426922466</v>
+        <v>51.95883667120654</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>30.96121252729515</v>
+        <v>8.065188823726652</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.4655846230089612</v>
+        <v>0.782691486916839</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0552204811399398</v>
+        <v>-0.0363407266569207</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6679</v>
+        <v>6486</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>206.0871308339404</v>
+        <v>209.5947783611973</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>192.5</v>
+        <v>77.7</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>37.28916436013965</v>
+        <v>39.93525947519911</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>12.51271994739064</v>
+        <v>34.33064005927103</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.122487128257296</v>
+        <v>0.8023927959619278</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.3334859672873069</v>
+        <v>-0.5262725775811985</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6803</v>
+        <v>6606</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>205.2193037402421</v>
+        <v>208.2924315520955</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>264</v>
+        <v>24.4</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>38.5837706827711</v>
+        <v>41.51374273511777</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>23.33763131521111</v>
+        <v>30.9612127435235</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.5307831076528505</v>
+        <v>0.4655846230089612</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.2254746880415861</v>
+        <v>-0.0552204812240594</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6732</v>
+        <v>6592</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>199.2100430862248</v>
+        <v>207.6056191949808</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>150.5</v>
+        <v>56.8</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>47.30896829259378</v>
+        <v>36.55200158431163</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>19.03168383190965</v>
+        <v>33.93720344191382</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.6598198957085418</v>
+        <v>0.5238698194250464</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.5686298176716372</v>
+        <v>-0.0525629958954667</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6790</v>
+        <v>6605</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>190.4585067073744</v>
+        <v>206.7073260876892</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>37.4</v>
+        <v>135</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>40.25523090998775</v>
+        <v>43.51522762342267</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>22.10788374966105</v>
+        <v>11.10049687111814</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5563429257858189</v>
+        <v>1.254306215525029</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0226859821670689</v>
+        <v>-0.297893791341113</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6592</v>
+        <v>6679</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>187.6056191949808</v>
+        <v>206.0871308339406</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>56.8</v>
+        <v>192.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>36.55200167543618</v>
+        <v>37.28916427437696</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>33.93720340885896</v>
+        <v>12.5127199727839</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5238698194250464</v>
+        <v>1.122487128257296</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0525629957993316</v>
+        <v>-0.333485967767992</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6720</v>
+        <v>6803</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>183.4170278560701</v>
+        <v>205.219303740242</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>110</v>
+        <v>264</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>41.91041807661064</v>
+        <v>38.58377058984399</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>14.00187981463155</v>
+        <v>23.33763131221368</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.741702785607006</v>
+        <v>0.5307831076528505</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.8334790511869687</v>
+        <v>-0.225474688281976</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6624</v>
+        <v>6625</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>182.8816772248316</v>
+        <v>202.8442373101634</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>37.35</v>
+        <v>75</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>50.41634624698776</v>
+        <v>54.08726524540144</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>4.557647517970557</v>
+        <v>13.48972547196288</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.8665847429039565</v>
+        <v>0.8746890340772676</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.1053416289069044</v>
+        <v>0.1439944320824181</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6573</v>
+        <v>6732</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>176.7200595420863</v>
+        <v>199.2100430862248</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>15.8</v>
+        <v>150.5</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.33530307685539</v>
+        <v>47.30896815081395</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16.78463977590926</v>
+        <v>19.03168379717791</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.7401970496020328</v>
+        <v>0.6598198957085418</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0201974352650441</v>
+        <v>0.5686298174312698</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6794</v>
+        <v>6790</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>174.3845286569956</v>
+        <v>190.4585067073744</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>70.7</v>
+        <v>37.4</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>39.98440863725326</v>
+        <v>40.25523092977399</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>14.38752564350983</v>
+        <v>22.10788378038853</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.023048600809997</v>
+        <v>0.5563429257858189</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.3781709680125299</v>
+        <v>-0.0226859821911086</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6552</v>
+        <v>6720</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>162.1497172619781</v>
+        <v>183.4170278560701</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>42.29435155823168</v>
+        <v>41.91041806551515</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>16.52592963529766</v>
+        <v>14.00187983614491</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.28961732823261</v>
+        <v>1.741702785607006</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0161780271176608</v>
+        <v>-0.8334790511869687</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6477</v>
+        <v>6624</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>154.3281328113852</v>
+        <v>182.8816772248316</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>33.25</v>
+        <v>37.35</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>42.20758604472604</v>
+        <v>50.41634557559575</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>17.90806122713255</v>
+        <v>4.557647315293847</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.4618441247406857</v>
+        <v>0.8665847429039565</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0617946611920654</v>
+        <v>-0.1053416204106767</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6546</v>
+        <v>6573</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>149.6000732478863</v>
+        <v>176.7200595420863</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>61.3</v>
+        <v>15.8</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>53.52130831126943</v>
+        <v>42.33530310062341</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>13.95041354839981</v>
+        <v>16.78463964305321</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.4831812445738822</v>
+        <v>0.7401970496020328</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.3402517597261525</v>
+        <v>0.0201974355053906</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6605</v>
+        <v>6794</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>146.7073260876892</v>
+        <v>174.3845286569957</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>135</v>
+        <v>70.7</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>43.51522760271236</v>
+        <v>39.98440871569621</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>11.10049678970176</v>
+        <v>14.38752566085559</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.254306215525029</v>
+        <v>1.023048600809997</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.2978937906200812</v>
+        <v>-0.3781709681807856</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6781,21 +6781,21 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6568</v>
+        <v>6477</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>103.4851529804437</v>
+        <v>154.3281328113852</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>129.5</v>
+        <v>33.25</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>39.49670406626338</v>
+        <v>42.20758615799335</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>17.31081758701804</v>
+        <v>17.90806128542718</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.4332688750984778</v>
+        <v>0.4618441247406857</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-1.222093735784944</v>
+        <v>-0.0617946614564438</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6625</v>
+        <v>6546</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>92.84423731016371</v>
+        <v>149.6000732478863</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>75</v>
+        <v>61.3</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>54.08726552836011</v>
+        <v>53.52130810355506</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>13.48972529546634</v>
+        <v>13.95041354865216</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.8746890340772676</v>
+        <v>0.4831812445738822</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.1439944317459194</v>
+        <v>0.3402517593656291</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6698</v>
+        <v>6568</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>85.43481518601371</v>
+        <v>103.4851529804396</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>30.7</v>
+        <v>129.5</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>41.80003016268667</v>
+        <v>39.49670404079745</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>11.95795600664137</v>
+        <v>17.31081756579558</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.940445290560841</v>
+        <v>0.4332688750984778</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0670112085901227</v>
+        <v>-1.222093736265626</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6680</v>
+        <v>6698</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>84.80145382472409</v>
+        <v>85.43481518601371</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>50.5</v>
+        <v>30.7</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>51.86727316328489</v>
+        <v>41.80003016704821</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>6.987106085145139</v>
+        <v>11.95795609910392</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.044923357110335</v>
+        <v>0.940445290560841</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,11 +6983,11 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.1442439727388986</v>
+        <v>-0.0670112087944135</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
